--- a/Cardiologie/Excel/cardio_8.xlsx
+++ b/Cardiologie/Excel/cardio_8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390AB489-77F5-40D5-BD16-C1AFDE13C9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E7CD0D-463C-46FA-A92A-A64CB1547CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,16 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="170">
-  <si>
-    <t>numero</t>
-  </si>
-  <si>
-    <t>proposition</t>
-  </si>
-  <si>
-    <t>reponse</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
   <si>
     <t>Les pathologies des troncs supra-aortiques incluent uniquement des lésions sténosantes des vaisseaux.</t>
   </si>
@@ -526,26 +517,33 @@
     <t>La morbi-mortalité doit être inférieure à 3% pour opérer une sténose carotidienne symptomatique.</t>
   </si>
   <si>
-    <t>Faux</t>
-  </si>
-  <si>
-    <t>Vrai</t>
+    <t>Numero</t>
+  </si>
+  <si>
+    <t>Proposition</t>
+  </si>
+  <si>
+    <t>Reponse</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>image</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -561,27 +559,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -590,11 +573,11 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -900,1839 +883,1851 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C166"/>
+  <dimension ref="A1:G166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="172.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="172.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C8" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C13" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C15" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C16" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C17" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C18" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C21" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C22" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C23" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C24" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C25" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C26" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C27" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C28" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="B29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C29" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C30" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C31" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C32" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C33" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C34" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C35" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="B36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C36" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="B37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C37" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="B38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C38" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="B39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C39" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="C40" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="B41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C41" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C42" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="B43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C43" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="B44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C44" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="B45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C45" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="B46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C46" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C47" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="B48" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C48" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="B49" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C49" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C50" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C51" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+      <c r="B52" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C52" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="B53" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C53" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+      <c r="B54" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C54" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+      <c r="B55" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C55" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+      <c r="B56" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C56" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+      <c r="B57" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C57" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="B58" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C58" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="B59" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C59" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+      <c r="B60" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C60" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+      <c r="B61" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C61" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+      <c r="B62" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C62" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+      <c r="B63" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C63" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+      <c r="B64" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C64" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+      <c r="B65" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C65" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+      <c r="B66" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C66" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="B67" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C67" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="B68" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C68" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="B69" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C69" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+      <c r="B70" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="C70" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="B71" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C71" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
+      <c r="B72" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="C72" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="B73" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C73" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+      <c r="B74" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C74" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="B75" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="C75" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+      <c r="B76" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="C76" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+      <c r="B77" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C77" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+      <c r="B78" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="C78" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+      <c r="B79" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="C79" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="B80" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C80" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
         <v>80</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="B81" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="C81" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
         <v>81</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+      <c r="B82" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="C82" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+      <c r="B83" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="C83" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
         <v>83</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
+      <c r="B84" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="C84" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
         <v>84</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+      <c r="B85" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="C85" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+      <c r="B86" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="C86" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
         <v>86</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
+      <c r="B87" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="C87" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
         <v>87</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+      <c r="B88" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="C88" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
         <v>88</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
+      <c r="B89" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C89" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
         <v>89</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+      <c r="B90" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="C90" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
         <v>90</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+      <c r="B91" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="C91" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
         <v>91</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+      <c r="B92" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="C92" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
         <v>92</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+      <c r="B93" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="C93" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
         <v>93</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
+      <c r="B94" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="C94" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
         <v>94</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+      <c r="B95" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="C95" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
         <v>95</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
+      <c r="B96" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="C96" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
         <v>96</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
+      <c r="B97" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="C97" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
         <v>97</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
+      <c r="B98" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="C98" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
         <v>98</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
+      <c r="B99" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="C99" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
         <v>99</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
+      <c r="B100" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="C100" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
         <v>100</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
+      <c r="B101" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="C101" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
         <v>101</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
+      <c r="B102" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C102" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
         <v>102</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
+      <c r="B103" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="C103" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
         <v>103</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
+      <c r="B104" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="C104" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
         <v>104</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
+      <c r="B105" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="C105" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
         <v>105</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
+      <c r="B106" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="C106" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
         <v>106</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
+      <c r="B107" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="C107" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
         <v>107</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
+      <c r="B108" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="C108" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
         <v>108</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
+      <c r="B109" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C109" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
         <v>109</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
+      <c r="B110" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="C110" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
         <v>110</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
+      <c r="B111" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="C111" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
         <v>111</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
+      <c r="B112" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="C112" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
         <v>112</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
+      <c r="B113" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="C113" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
         <v>113</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
+      <c r="B114" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C114" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
         <v>114</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
+      <c r="B115" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C115" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
         <v>115</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
+      <c r="B116" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="C116" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
         <v>116</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="2">
+      <c r="B117" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C117" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
         <v>117</v>
       </c>
-      <c r="C116" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
+      <c r="B118" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="C118" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
         <v>118</v>
       </c>
-      <c r="C117" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
+      <c r="B119" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="C119" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
         <v>119</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
+      <c r="B120" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C120" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
         <v>120</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
+      <c r="B121" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="C121" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
         <v>121</v>
       </c>
-      <c r="C120" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
+      <c r="B122" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="C122" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
         <v>122</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
+      <c r="B123" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="C123" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
         <v>123</v>
       </c>
-      <c r="C122" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
+      <c r="B124" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="C124" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
         <v>124</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
+      <c r="B125" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="C125" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
         <v>125</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
+      <c r="B126" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C126" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
         <v>126</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
+      <c r="B127" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="C127" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
         <v>127</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="2">
+      <c r="B128" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="C128" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
         <v>128</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
+      <c r="B129" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="C129" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
         <v>129</v>
       </c>
-      <c r="C128" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
+      <c r="B130" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="C130" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
         <v>130</v>
       </c>
-      <c r="C129" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
+      <c r="B131" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="C131" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
         <v>131</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
+      <c r="B132" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="C132" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
         <v>132</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
+      <c r="B133" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="C133" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
         <v>133</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
+      <c r="B134" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="C134" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
         <v>134</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="2">
+      <c r="B135" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="C135" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
         <v>135</v>
       </c>
-      <c r="C134" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
+      <c r="B136" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="C136" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
         <v>136</v>
       </c>
-      <c r="C135" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="2">
+      <c r="B137" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="C137" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
         <v>137</v>
       </c>
-      <c r="C136" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
+      <c r="B138" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="C138" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
         <v>138</v>
       </c>
-      <c r="C137" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
+      <c r="B139" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C139" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
         <v>139</v>
       </c>
-      <c r="C138" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="2">
+      <c r="B140" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="C140" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
         <v>140</v>
       </c>
-      <c r="C139" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
+      <c r="B141" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="C141" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
         <v>141</v>
       </c>
-      <c r="C140" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="2">
+      <c r="B142" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="C142" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
         <v>142</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="2">
+      <c r="B143" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="C143" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
         <v>143</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="2">
+      <c r="B144" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="C144" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
         <v>144</v>
       </c>
-      <c r="C143" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="2">
+      <c r="B145" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="C145" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
         <v>145</v>
       </c>
-      <c r="C144" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="2">
+      <c r="B146" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="C146" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
         <v>146</v>
       </c>
-      <c r="C145" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="2">
+      <c r="B147" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="C147" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
         <v>147</v>
       </c>
-      <c r="C146" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
+      <c r="B148" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="C148" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
         <v>148</v>
       </c>
-      <c r="C147" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="2">
+      <c r="B149" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="C149" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
         <v>149</v>
       </c>
-      <c r="C148" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="2">
+      <c r="B150" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="C150" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
         <v>150</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="2">
+      <c r="B151" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="C151" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
         <v>151</v>
       </c>
-      <c r="C150" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="2">
+      <c r="B152" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="C152" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
         <v>152</v>
       </c>
-      <c r="C151" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="2">
+      <c r="B153" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="C153" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
         <v>153</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="2">
+      <c r="B154" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="C154" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
         <v>154</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="2">
+      <c r="B155" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="C155" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
         <v>155</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
+      <c r="B156" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="C156" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
         <v>156</v>
       </c>
-      <c r="C155" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
+      <c r="B157" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B156" s="2" t="s">
+      <c r="C157" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
         <v>157</v>
       </c>
-      <c r="C156" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="2">
+      <c r="B158" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B157" s="2" t="s">
+      <c r="C158" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
         <v>158</v>
       </c>
-      <c r="C157" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
+      <c r="B159" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="C159" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
         <v>159</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
+      <c r="B160" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="C160" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
         <v>160</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="2">
+      <c r="B161" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B160" s="2" t="s">
+      <c r="C161" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
         <v>161</v>
       </c>
-      <c r="C160" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="2">
+      <c r="B162" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B161" s="2" t="s">
+      <c r="C162" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
         <v>162</v>
       </c>
-      <c r="C161" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="2">
+      <c r="B163" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="C163" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
         <v>163</v>
       </c>
-      <c r="C162" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="2">
+      <c r="B164" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="C164" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
         <v>164</v>
       </c>
-      <c r="C163" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="2">
+      <c r="B165" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="C165" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
         <v>165</v>
       </c>
-      <c r="C164" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="2">
+      <c r="B166" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
-        <v>165</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>168</v>
+      <c r="C166" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Cardiologie/Excel/cardio_8.xlsx
+++ b/Cardiologie/Excel/cardio_8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E7CD0D-463C-46FA-A92A-A64CB1547CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E50647-09CA-4E3D-923C-17E2B28DE435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="338">
   <si>
     <t>Les pathologies des troncs supra-aortiques incluent uniquement des lésions sténosantes des vaisseaux.</t>
   </si>
@@ -536,6 +536,504 @@
   </si>
   <si>
     <t>image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles incluent également les dissections et les tumeurs du glomus carotidien </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'athérome est cité comme l'étiologie principale de ces pathologies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le polygone de Willis est l'une des voies anastomotiques de suppléance citées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont le plus souvent d'origine athéroscléreuse, mais d'autres causes existent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La majorité des sténoses sont asymptomatiques et détectées par Doppler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les AIT sont définis par une durée inférieure à 24 heures </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La durée d'un AIT est inférieure à 24 heures (et non 12h) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le bilan préopératoire de pontage est un exemple de mode de découverte cité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le caractère opérateur-dépendant est listé comme une limite de cet examen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'un des avantages cités pour l'échographie-Doppler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angiographie conventionnelle est l'examen cité pour l'étude de ces artères </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement endoluminal ne présente pas ce risque, contrairement à la chirurgie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'IRM permet effectivement de détecter ces signes au niveau de la plaque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'athérome est l'étiologie principale, pas les tumeurs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le confluent vertébrobasilaire fait partie des voies de suppléance énumérées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La définition d'un AIT est un accident ischémique de durée inférieure à 24 heures </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il permet l'étude de la paroi ET l'étude hémodynamique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'échographie-Doppler est l'examen de premier choix </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est supérieure pour les patients asymptomatiques et ceux de plus de 70 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est un mode fréquent de découverte mentionné pour ces sténoses </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles causent environ 15 % des AVC (et non 50 %) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles siègent surtout à la bifurcation carotidienne ou au siphon carotidien </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une limite explicitement mentionnée pour cette technique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement est suggéré si l'espérance de vie est supérieure à 5 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'athérosclérose est décrite comme l'étiologie de loin la plus fréquente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La compression extrinsèque positionnelle est citée parmi les étiologies principales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce mécanisme est au contraire cité comme étant souvent à l'origine de l'accident </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les mouvements de tête sont listés comme facteur favorisant une baisse de débit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils peuvent être d'origine hémodynamique ou thromboembolique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise qu'elles sont au contraire le plus souvent asymptomatiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le mode de découverte fortuit cité par le texte </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est un symptôme de sténose sous-clavière et non carotidienne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Des symptômes comme la claudication ou l'AIT sont décrits pour ces lésions </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles peuvent effectivement causer des AIT dans le territoire carotidien </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La majorité des dissections surviennent spontanément </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce sont des symptômes caractéristiques cités pour la carotide interne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il est désigné comme l'examen de choix en première intention </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'IRM cérébrale permet au contraire de visualiser l'hématome de paroi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angiographie est la méthode de référence mais n'est pas décrite comme obligatoire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles se développent dans l'adventice du vaisseau et non dans l'intima </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces tumeurs sont décrites comme étant généralement bénignes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne la découverte possible de tuméfactions asymptomatiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles peuvent effectivement se présenter comme une tuméfaction battante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'athérosclérose est de loin l'étiologie la plus fréquente de ces accidents </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dissection est la première cause d'ischémie cérébrale pour cette tranche d'âge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme qu'il s'agit de tumeurs très vascularisées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles surviennent le plus souvent entre 40 et 60 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que la majorité des cas surviennent spontanément </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le délai d'apparition varie de quelques heures à un mois </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est au contraire l'examen de choix en première intention </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La radiothérapie est listée comme une étiologie possible des sténoses </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise qu'elles causent environ 15 % des AVC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La bifurcation et le siphon sont les deux sièges de prédilection mentionnés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un souffle à l'auscultation est au contraire souvent à l'origine de leur découverte </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces phénomènes sont bien à l'origine d'emboles fibrinoplaquettaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cela survient uniquement en cas de sténoses serrées (et non peu serrées) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une manifestation d'un AIT et non d'un AVC constitué </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'une des manifestations cliniques principales de l'AVC mentionnées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte mentionne une monoplégie d'un membre inférieur, pas une paraplégie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les troubles du langage (ou aphasie) sont cités pour les deux types d'accidents </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hémi-parésie et l'hémi-paresthésie sont controlatérales à la lésion carotidienne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'amaurose fugace est une manifestation ipsilatérale à la lésion carotidienne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces manifestations cliniques sont listées parmi les signes de l'AVC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un accident ischémique se manifeste par un déficit neurologique focal/latéralisé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diagnostic différentiel de l'AIT inclut l'hypoglycémie et non l'hyperglycémie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces trois pathologies sont citées comme diagnostics différentiels de l'AVC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les emboles d'origine cardiaque représentent environ 30 % des cas (et non 50 %) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'athérosclérose des vaisseaux de grand et moyen calibre est en cause dans 15-20 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est responsable d'environ 20 % des AVC chez les patients de moins de 50 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont définis par l'obstruction d'un vaisseau de petit calibre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une étiologie rare d'AVC, sans précision du profil type de patient dans le texte </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces causes sont listées parmi les étiologies rares d'AVC ischémique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'échographie-Doppler est explicitement désignée comme l'examen de premier choix </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'obésité et les calcifications volumineuses sont des limites citées de cet examen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'étude hémodynamique par Doppler permet de dépister la sténose (qui accélère le flux) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le dépistage est recommandé chez les patients porteurs de ces pathologies vasculaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On réalise l'examen avant une chirurgie cardiaque (bilan préopératoire) et non après </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen de référence est l'angiographie conventionnelle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angiographie nécessite au contraire une injection par voie artérielle (souvent fémorale) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les complications neurologiques sont une limite mentionnée pour cet examen invasif </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le scanner avec contraste qui permet de détecter cette rupture </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angiographie par RM permet au contraire l'étude du polygone de Willis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angiographie par RM permet effectivement l'étude du parenchyme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'angiographie par RM qui a tendance à surestimer les sténoses serrées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il permet de visualiser l'ischémie et d'exclure les hémorragies ou tumeurs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'estimation précise du pourcentage de sténose est parfois difficile par angio-scanner </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le contrôle des facteurs de risque et les antiagrégants sont les bases du traitement préventif </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la technique chirurgicale de référence pour traiter la sténose carotidienne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'absence de nécessité d'anesthésie est un avantage cité du traitement endoluminal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document liste précisément ces complications postopératoires pour la chirurgie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une bifurcation haute est un facteur augmentant le risque chirurgical, favorisant l'endoluminal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'endoluminal est l'option privilégiée dans ces situations à haut risque chirurgical </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La morbi-mortalité du traitement endoluminal est au contraire supérieure à celle de la chirurgie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement est recommandé si la sténose est supérieure ou égale à 70 % </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La morbi-mortalité postopératoire doit effectivement être inférieure à 3 % dans ce cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On l'opère si le risque d'AVC est ipsilatéral (même côté que la lésion) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le seuil de sténose recommandé pour le traitement chirurgical ou suggéré est de 70 % </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présence d'une lésion controlatérale augmente effectivement le risque d'AVC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le Doppler transcrânien (et non l'IRM) qui est cité pour détecter les micro-emboles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une baisse de la réserve vasculaire cérébrale est un facteur de risque d'AVC plus élevé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'IRM permet effectivement de détecter la rupture de la cape fibreuse de la plaque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'Echo-Doppler est utilisé pour analyser la structure de la plaque (ulcérée, irrégulière) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont cités comme étiologies d'accidents vertébrobasilaires, pas carotidiens </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie de Takayasu est citée parmi les étiologies rares d'accidents ischémiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les symptômes hémodynamiques nécessitent une atteinte bilatérale ou une hypoplasie importante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces facteurs sont listés comme favorisant le mécanisme hémodynamique de l'accident </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils peuvent être causés par des emboles cardiaques ou de l'aorte ascendante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que la plupart de ces lésions sont découvertes par hasard </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le scanner est effectivement décrit comme ayant un intérêt limité pour ces lésions </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'IRM est l'examen permettant de visualiser ces lésions ischémiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les troubles visuels incluent la diplopie ou l'hémianopsie, mais l'amaurose est bilatérale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le drop-attack est une manifestation de l'insuffisance vertébrobasilaire, pas carotidienne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une des manifestations cliniques possibles de l'insuffisance vertébrobasilaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angio-IRM explore au contraire mal les artères vertébrales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est décrite comme un examen indispensable avant toute intervention </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La chirurgie est au contraire exceptionnellement indiquée pour ces lésions </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme cette localisation fréquente à l'origine des troncs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En cas de double atteinte, le traitement de la carotide peut améliorer les symptômes vertébraux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'artère sous-clavière gauche qui est la plus fréquemment touchée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le tronc brachio-céphalique est effectivement plus fréquemment touché que les carotides primitives </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen clinique montre une asymétrie de pulsatilité ou de tension artérielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La physiopathologie inclut des lésions ischémiques distales d’origine embolique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le vol vertébral survient en cas de sténose de l'artère sous-clavière (pas carotidienne) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont au contraire le plus souvent asymptomatiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome de vol sous-clavier est effectivement le plus souvent bien toléré </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome donne des symptômes vertébrobasilaires provoqués par l'utilisation du bras </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte mentionne le vol vertébral, ce qui correspond à une inversion de flux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen clinique peut au contraire montrer un souffle dans diverses régions </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les examens complémentaires sont indiqués uniquement chez les patients symptomatiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En cas de sténose asymptomatique, il n'y a effectivement pas de traitement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'écho-Doppler permet l'objectivation de la sténose et la recherche de vol vertébral </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces lésions entraînent une insuffisance artérielle du membre supérieur droit (pas gauche) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il n'y a pas de traitement recommandé pour les sténoses asymptomatiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement chirurgical peut effectivement consister en une greffe veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La physiopathologie du tronc brachio-céphalique inclut l'insuffisance vertébrobasilaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut effectivement causer des accidents ischémiques dans le territoire carotidien </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement endovasculaire de ce tronc présente un risque d’emboles cérébraux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans la majorité des cas, la dissection survient au contraire spontanément </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les accidents surviennent souvent dans le territoire de l'artère sylvienne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La déchirure peut être entre intima/média ou entre média/adventice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les maladies du tissu élastique (Marfan) et la dysplasie sont des facteurs favorisants </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l’hématome sous-adventiciel (et non sous-intimal) qui augmente le calibre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dissection artérielle peut effectivement évoluer vers un pseudo-anévrisme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l’hématome sous-intimal (et non sous-adventitiel) qui entraîne une sténose </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les signes d’ischémie cérébrale secondaire surviennent dans ce délai </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les signes locaux incluent des compressions des structures avoisinantes et des douleurs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la dissection de la carotide interne qui peut causer une atteinte de nerfs crâniens </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une hémorragie méningée est possible en cas de dissection intracrânienne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angio-RM peut montrer un hématome ou une absence de visualisation du vaisseau </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'angiographie conventionnelle qui montre cet aspect "en flamme de bougie" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angiographie conventionnelle montre effectivement des sténoses longues et irrégulières </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angiographie conventionnelle permet le diagnostic d’une dysplasie sous-jacente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'écho-Doppler est l'examen de premier choix, mais l'angiographie est la référence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'écho-Doppler permet effectivement de visualiser ces trois éléments </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si pas de signes d’ischémie cérébrale, le traitement est effectivement antiplaquettaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En cas d'accident ischémique constitué, le traitement est thrombolytique ou chirurgical </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle touche les hommes ou les femmes, le document ne précise pas de préférence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document liste précisément ces symptômes liés aux nerfs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'imagerie montre un « blush » tumoral lié à une riche vascularisation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement recommandé est effectivement l'exérèse chirurgicale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'imagerie (IRM, Doppler, angiographie) confirme le diagnostic par un « blush » </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour une sténose asymptomatique, le seuil de morbi-mortalité requis est &lt; 3 % </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le seuil de sténose recommandé pour le traitement chirurgical est de ≥ 70 % </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement est effectivement suggéré si l'espérance de vie est &gt; 5 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour une sténose symptomatique, le seuil de morbi-mortalité requis est &lt; 6 % </t>
+  </si>
+  <si>
+    <t>Page</t>
   </si>
 </sst>
 </file>
@@ -883,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G166"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
@@ -892,7 +1390,7 @@
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>165</v>
       </c>
@@ -906,16 +1404,19 @@
         <v>168</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -925,8 +1426,14 @@
       <c r="C2" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -936,8 +1443,14 @@
       <c r="C3" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -947,8 +1460,14 @@
       <c r="C4" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -958,8 +1477,14 @@
       <c r="C5" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -969,8 +1494,14 @@
       <c r="C6" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -980,8 +1511,14 @@
       <c r="C7" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -991,8 +1528,14 @@
       <c r="C8" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1002,8 +1545,14 @@
       <c r="C9" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1013,8 +1562,14 @@
       <c r="C10" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1024,8 +1579,14 @@
       <c r="C11" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1035,8 +1596,14 @@
       <c r="C12" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1046,8 +1613,14 @@
       <c r="C13" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E13" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1057,8 +1630,14 @@
       <c r="C14" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1068,8 +1647,14 @@
       <c r="C15" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1079,8 +1664,14 @@
       <c r="C16" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1090,8 +1681,14 @@
       <c r="C17" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>187</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1101,8 +1698,14 @@
       <c r="C18" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1112,8 +1715,14 @@
       <c r="C19" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1123,8 +1732,14 @@
       <c r="C20" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>190</v>
+      </c>
+      <c r="E20" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1134,8 +1749,14 @@
       <c r="C21" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1145,8 +1766,14 @@
       <c r="C22" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>192</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1156,8 +1783,14 @@
       <c r="C23" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1167,8 +1800,14 @@
       <c r="C24" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>194</v>
+      </c>
+      <c r="E24" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1178,8 +1817,14 @@
       <c r="C25" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>195</v>
+      </c>
+      <c r="E25" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1189,8 +1834,14 @@
       <c r="C26" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>196</v>
+      </c>
+      <c r="E26" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1200,8 +1851,14 @@
       <c r="C27" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>197</v>
+      </c>
+      <c r="E27" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1211,8 +1868,14 @@
       <c r="C28" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>198</v>
+      </c>
+      <c r="E28" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1222,8 +1885,14 @@
       <c r="C29" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>199</v>
+      </c>
+      <c r="E29" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1233,8 +1902,14 @@
       <c r="C30" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>200</v>
+      </c>
+      <c r="E30" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1244,8 +1919,14 @@
       <c r="C31" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>201</v>
+      </c>
+      <c r="E31" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1255,8 +1936,14 @@
       <c r="C32" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>202</v>
+      </c>
+      <c r="E32" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1266,8 +1953,14 @@
       <c r="C33" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>203</v>
+      </c>
+      <c r="E33" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1277,8 +1970,14 @@
       <c r="C34" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>204</v>
+      </c>
+      <c r="E34" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1288,8 +1987,14 @@
       <c r="C35" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>205</v>
+      </c>
+      <c r="E35" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1299,8 +2004,14 @@
       <c r="C36" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>206</v>
+      </c>
+      <c r="E36" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1310,8 +2021,14 @@
       <c r="C37" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>207</v>
+      </c>
+      <c r="E37" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1321,8 +2038,14 @@
       <c r="C38" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>208</v>
+      </c>
+      <c r="E38" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1332,8 +2055,14 @@
       <c r="C39" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>209</v>
+      </c>
+      <c r="E39" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1343,8 +2072,14 @@
       <c r="C40" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>210</v>
+      </c>
+      <c r="E40" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1354,8 +2089,14 @@
       <c r="C41" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>211</v>
+      </c>
+      <c r="E41" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1365,8 +2106,14 @@
       <c r="C42" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>212</v>
+      </c>
+      <c r="E42" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1376,8 +2123,14 @@
       <c r="C43" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>213</v>
+      </c>
+      <c r="E43" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1387,8 +2140,14 @@
       <c r="C44" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>214</v>
+      </c>
+      <c r="E44" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1398,8 +2157,14 @@
       <c r="C45" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>215</v>
+      </c>
+      <c r="E45" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1409,8 +2174,14 @@
       <c r="C46" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>216</v>
+      </c>
+      <c r="E46" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1420,8 +2191,14 @@
       <c r="C47" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>217</v>
+      </c>
+      <c r="E47" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1431,8 +2208,14 @@
       <c r="C48" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>218</v>
+      </c>
+      <c r="E48" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1442,8 +2225,14 @@
       <c r="C49" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>219</v>
+      </c>
+      <c r="E49" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1453,8 +2242,14 @@
       <c r="C50" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>220</v>
+      </c>
+      <c r="E50" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1464,8 +2259,14 @@
       <c r="C51" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>221</v>
+      </c>
+      <c r="E51" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1475,8 +2276,14 @@
       <c r="C52" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>222</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1486,8 +2293,14 @@
       <c r="C53" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>223</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -1497,8 +2310,14 @@
       <c r="C54" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>224</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1508,8 +2327,14 @@
       <c r="C55" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>225</v>
+      </c>
+      <c r="E55" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1519,8 +2344,14 @@
       <c r="C56" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>226</v>
+      </c>
+      <c r="E56" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1530,8 +2361,14 @@
       <c r="C57" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>227</v>
+      </c>
+      <c r="E57" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1541,8 +2378,14 @@
       <c r="C58" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>228</v>
+      </c>
+      <c r="E58" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1552,8 +2395,14 @@
       <c r="C59" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>229</v>
+      </c>
+      <c r="E59" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1563,8 +2412,14 @@
       <c r="C60" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>230</v>
+      </c>
+      <c r="E60" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1574,8 +2429,14 @@
       <c r="C61" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>231</v>
+      </c>
+      <c r="E61" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -1585,8 +2446,14 @@
       <c r="C62" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>232</v>
+      </c>
+      <c r="E62" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1596,8 +2463,14 @@
       <c r="C63" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>233</v>
+      </c>
+      <c r="E63" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -1607,8 +2480,14 @@
       <c r="C64" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>234</v>
+      </c>
+      <c r="E64" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -1618,8 +2497,14 @@
       <c r="C65" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>235</v>
+      </c>
+      <c r="E65" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -1629,8 +2514,14 @@
       <c r="C66" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>236</v>
+      </c>
+      <c r="E66" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -1640,8 +2531,14 @@
       <c r="C67" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>237</v>
+      </c>
+      <c r="E67" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -1651,8 +2548,14 @@
       <c r="C68" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>238</v>
+      </c>
+      <c r="E68" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -1662,8 +2565,14 @@
       <c r="C69" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>239</v>
+      </c>
+      <c r="E69" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -1673,8 +2582,14 @@
       <c r="C70" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>240</v>
+      </c>
+      <c r="E70" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -1684,8 +2599,14 @@
       <c r="C71" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>241</v>
+      </c>
+      <c r="E71" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -1695,8 +2616,14 @@
       <c r="C72" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>242</v>
+      </c>
+      <c r="E72" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -1706,8 +2633,14 @@
       <c r="C73" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>243</v>
+      </c>
+      <c r="E73" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -1717,8 +2650,14 @@
       <c r="C74" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>244</v>
+      </c>
+      <c r="E74" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -1728,8 +2667,14 @@
       <c r="C75" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>245</v>
+      </c>
+      <c r="E75" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -1739,8 +2684,14 @@
       <c r="C76" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>246</v>
+      </c>
+      <c r="E76" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -1750,8 +2701,14 @@
       <c r="C77" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>247</v>
+      </c>
+      <c r="E77" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -1761,8 +2718,14 @@
       <c r="C78" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>248</v>
+      </c>
+      <c r="E78" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -1772,8 +2735,14 @@
       <c r="C79" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>249</v>
+      </c>
+      <c r="E79" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -1783,8 +2752,14 @@
       <c r="C80" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>250</v>
+      </c>
+      <c r="E80" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -1794,8 +2769,14 @@
       <c r="C81" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>251</v>
+      </c>
+      <c r="E81" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -1805,8 +2786,14 @@
       <c r="C82" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>252</v>
+      </c>
+      <c r="E82" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -1816,8 +2803,14 @@
       <c r="C83" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>253</v>
+      </c>
+      <c r="E83" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -1827,8 +2820,14 @@
       <c r="C84" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>254</v>
+      </c>
+      <c r="E84" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -1838,8 +2837,14 @@
       <c r="C85" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>255</v>
+      </c>
+      <c r="E85" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -1849,8 +2854,14 @@
       <c r="C86" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>256</v>
+      </c>
+      <c r="E86" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -1860,8 +2871,14 @@
       <c r="C87" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>257</v>
+      </c>
+      <c r="E87" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -1871,8 +2888,14 @@
       <c r="C88" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>258</v>
+      </c>
+      <c r="E88" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -1882,8 +2905,14 @@
       <c r="C89" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
+        <v>259</v>
+      </c>
+      <c r="E89" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -1893,8 +2922,14 @@
       <c r="C90" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>260</v>
+      </c>
+      <c r="E90" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -1904,8 +2939,14 @@
       <c r="C91" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>261</v>
+      </c>
+      <c r="E91" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -1915,8 +2956,14 @@
       <c r="C92" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>262</v>
+      </c>
+      <c r="E92" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -1926,8 +2973,14 @@
       <c r="C93" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>263</v>
+      </c>
+      <c r="E93" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -1937,8 +2990,14 @@
       <c r="C94" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>264</v>
+      </c>
+      <c r="E94" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -1948,8 +3007,14 @@
       <c r="C95" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>265</v>
+      </c>
+      <c r="E95" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -1959,8 +3024,14 @@
       <c r="C96" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>266</v>
+      </c>
+      <c r="E96" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -1970,8 +3041,14 @@
       <c r="C97" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>267</v>
+      </c>
+      <c r="E97" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -1981,8 +3058,14 @@
       <c r="C98" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>268</v>
+      </c>
+      <c r="E98" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -1992,8 +3075,14 @@
       <c r="C99" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>269</v>
+      </c>
+      <c r="E99" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -2003,8 +3092,14 @@
       <c r="C100" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>270</v>
+      </c>
+      <c r="E100" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -2014,8 +3109,14 @@
       <c r="C101" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>271</v>
+      </c>
+      <c r="E101" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -2025,8 +3126,14 @@
       <c r="C102" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>272</v>
+      </c>
+      <c r="E102" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -2036,8 +3143,14 @@
       <c r="C103" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>273</v>
+      </c>
+      <c r="E103" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -2047,8 +3160,14 @@
       <c r="C104" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>274</v>
+      </c>
+      <c r="E104" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -2058,8 +3177,14 @@
       <c r="C105" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>275</v>
+      </c>
+      <c r="E105" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -2069,8 +3194,14 @@
       <c r="C106" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>276</v>
+      </c>
+      <c r="E106" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -2080,8 +3211,14 @@
       <c r="C107" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>277</v>
+      </c>
+      <c r="E107" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -2091,8 +3228,14 @@
       <c r="C108" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>278</v>
+      </c>
+      <c r="E108" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -2102,8 +3245,14 @@
       <c r="C109" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>279</v>
+      </c>
+      <c r="E109" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -2113,8 +3262,14 @@
       <c r="C110" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>280</v>
+      </c>
+      <c r="E110" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -2124,8 +3279,14 @@
       <c r="C111" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>281</v>
+      </c>
+      <c r="E111" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -2135,8 +3296,14 @@
       <c r="C112" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>282</v>
+      </c>
+      <c r="E112" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -2146,8 +3313,14 @@
       <c r="C113" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>283</v>
+      </c>
+      <c r="E113" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -2157,8 +3330,14 @@
       <c r="C114" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>284</v>
+      </c>
+      <c r="E114" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -2168,8 +3347,14 @@
       <c r="C115" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>285</v>
+      </c>
+      <c r="E115" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -2179,8 +3364,14 @@
       <c r="C116" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>286</v>
+      </c>
+      <c r="E116" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -2190,8 +3381,14 @@
       <c r="C117" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>287</v>
+      </c>
+      <c r="E117" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -2201,8 +3398,14 @@
       <c r="C118" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" t="s">
+        <v>288</v>
+      </c>
+      <c r="E118" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -2212,8 +3415,14 @@
       <c r="C119" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" t="s">
+        <v>289</v>
+      </c>
+      <c r="E119" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -2223,8 +3432,14 @@
       <c r="C120" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
+        <v>290</v>
+      </c>
+      <c r="E120" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -2234,8 +3449,14 @@
       <c r="C121" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
+        <v>291</v>
+      </c>
+      <c r="E121" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -2245,8 +3466,14 @@
       <c r="C122" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" t="s">
+        <v>292</v>
+      </c>
+      <c r="E122" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -2256,8 +3483,14 @@
       <c r="C123" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
+        <v>293</v>
+      </c>
+      <c r="E123" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -2267,8 +3500,14 @@
       <c r="C124" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>294</v>
+      </c>
+      <c r="E124" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -2278,8 +3517,14 @@
       <c r="C125" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>295</v>
+      </c>
+      <c r="E125" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -2289,8 +3534,14 @@
       <c r="C126" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>296</v>
+      </c>
+      <c r="E126" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -2300,8 +3551,14 @@
       <c r="C127" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
+        <v>297</v>
+      </c>
+      <c r="E127" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -2311,8 +3568,14 @@
       <c r="C128" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
+        <v>298</v>
+      </c>
+      <c r="E128" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -2322,8 +3585,14 @@
       <c r="C129" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
+        <v>299</v>
+      </c>
+      <c r="E129" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -2333,8 +3602,14 @@
       <c r="C130" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
+        <v>300</v>
+      </c>
+      <c r="E130" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -2344,8 +3619,14 @@
       <c r="C131" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" t="s">
+        <v>301</v>
+      </c>
+      <c r="E131" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -2355,8 +3636,14 @@
       <c r="C132" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
+        <v>302</v>
+      </c>
+      <c r="E132" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -2366,8 +3653,14 @@
       <c r="C133" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
+        <v>303</v>
+      </c>
+      <c r="E133" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -2377,8 +3670,14 @@
       <c r="C134" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
+        <v>304</v>
+      </c>
+      <c r="E134" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -2388,8 +3687,14 @@
       <c r="C135" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" t="s">
+        <v>305</v>
+      </c>
+      <c r="E135" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -2399,8 +3704,14 @@
       <c r="C136" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136" t="s">
+        <v>306</v>
+      </c>
+      <c r="E136" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -2410,8 +3721,14 @@
       <c r="C137" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>307</v>
+      </c>
+      <c r="E137" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -2421,8 +3738,14 @@
       <c r="C138" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" t="s">
+        <v>308</v>
+      </c>
+      <c r="E138" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -2432,8 +3755,14 @@
       <c r="C139" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
+        <v>309</v>
+      </c>
+      <c r="E139" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -2443,8 +3772,14 @@
       <c r="C140" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" t="s">
+        <v>310</v>
+      </c>
+      <c r="E140" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -2454,8 +3789,14 @@
       <c r="C141" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141" t="s">
+        <v>311</v>
+      </c>
+      <c r="E141" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -2465,8 +3806,14 @@
       <c r="C142" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
+        <v>312</v>
+      </c>
+      <c r="E142" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -2476,8 +3823,14 @@
       <c r="C143" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143" t="s">
+        <v>313</v>
+      </c>
+      <c r="E143" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -2487,8 +3840,14 @@
       <c r="C144" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144" t="s">
+        <v>314</v>
+      </c>
+      <c r="E144" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -2498,8 +3857,14 @@
       <c r="C145" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
+        <v>315</v>
+      </c>
+      <c r="E145" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -2509,8 +3874,14 @@
       <c r="C146" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146" t="s">
+        <v>316</v>
+      </c>
+      <c r="E146" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -2520,8 +3891,14 @@
       <c r="C147" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147" t="s">
+        <v>317</v>
+      </c>
+      <c r="E147" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -2531,8 +3908,14 @@
       <c r="C148" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148" t="s">
+        <v>318</v>
+      </c>
+      <c r="E148" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -2542,8 +3925,14 @@
       <c r="C149" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149" t="s">
+        <v>319</v>
+      </c>
+      <c r="E149" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -2553,8 +3942,14 @@
       <c r="C150" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
+        <v>320</v>
+      </c>
+      <c r="E150" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -2564,8 +3959,14 @@
       <c r="C151" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" t="s">
+        <v>321</v>
+      </c>
+      <c r="E151" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -2575,8 +3976,14 @@
       <c r="C152" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
+        <v>322</v>
+      </c>
+      <c r="E152" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -2586,8 +3993,14 @@
       <c r="C153" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" t="s">
+        <v>323</v>
+      </c>
+      <c r="E153" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -2597,8 +4010,14 @@
       <c r="C154" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154" t="s">
+        <v>324</v>
+      </c>
+      <c r="E154" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -2608,8 +4027,14 @@
       <c r="C155" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D155" t="s">
+        <v>325</v>
+      </c>
+      <c r="E155" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -2619,8 +4044,14 @@
       <c r="C156" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156" t="s">
+        <v>326</v>
+      </c>
+      <c r="E156" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -2630,8 +4061,14 @@
       <c r="C157" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157" t="s">
+        <v>327</v>
+      </c>
+      <c r="E157" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -2641,8 +4078,14 @@
       <c r="C158" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>328</v>
+      </c>
+      <c r="E158" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -2652,8 +4095,14 @@
       <c r="C159" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159" t="s">
+        <v>329</v>
+      </c>
+      <c r="E159" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -2663,8 +4112,14 @@
       <c r="C160" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160" t="s">
+        <v>330</v>
+      </c>
+      <c r="E160" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -2674,8 +4129,14 @@
       <c r="C161" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161" t="s">
+        <v>331</v>
+      </c>
+      <c r="E161" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -2685,8 +4146,14 @@
       <c r="C162" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162" t="s">
+        <v>332</v>
+      </c>
+      <c r="E162" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -2696,8 +4163,14 @@
       <c r="C163" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163" t="s">
+        <v>333</v>
+      </c>
+      <c r="E163" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -2707,8 +4180,14 @@
       <c r="C164" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164" t="s">
+        <v>334</v>
+      </c>
+      <c r="E164" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -2718,8 +4197,14 @@
       <c r="C165" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165" t="s">
+        <v>335</v>
+      </c>
+      <c r="E165" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -2728,6 +4213,12 @@
       </c>
       <c r="C166" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="D166" t="s">
+        <v>336</v>
+      </c>
+      <c r="E166" s="1">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
